--- a/content/tz-kak-zapominat-ieroglify.xlsx
+++ b/content/tz-kak-zapominat-ieroglify.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Как запоминать иероглифы, если через две недели знак снова кажется незнакомым. Разбираем две причины, по которым это происходит: вы путаете узнавание со знанием и учите знаки поодиночке, хотя в китайском почти всё — слова из двух знаков. Показываем, сколько знаков в день реально запомнить, когда к ним возвращаться и как проверить себя за две минуты.</t>
+          <t>Как запоминать иероглифы, если через две недели знак снова кажется незнакомым. Причины обычно две. Первая: вы узнали знак в тексте и решили, что выучили, — а узнать и написать это разные вещи. Вторая: вы учите знаки по одному, хотя в китайском почти каждое слово состоит из двух. Рассказываем, сколько знаков в день реально запомнить, когда к ним возвращаться и как проверить себя за две минуты.</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>39 045 знаков (лимит ≈ 50 000)</t>
+          <t>39 114 знаков (лимит ≈ 50 000)</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>26,1 % (норма 26–31 %)</t>
+          <t>26,2 % (норма 26–31 %)</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>36,7 %; FAQ на 65,8 %</t>
+          <t>37,0 %; FAQ на 66,0 %</t>
         </is>
       </c>
     </row>
@@ -1375,18 +1375,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="54" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Предлоги, падежи и язык</t>
+          <t>Второй большой проход: текст был слишком плотным</t>
         </is>
       </c>
     </row>
@@ -1410,68 +1410,238 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>«в разборе ПРО ЗА какое время реально выучить китайский»</t>
+          <t>ПАСПОРТ: «Обычно спрашивают про приём: какой способ запоминания самый действенный… Люди, которые жалуются, что знаки не держатся, чаще всего делают две другие ошибки: принимают узнавание за знание и учат знаки поодиночке, хотя…»</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>«в разборе о том, за какое время реально выучить китайский»</t>
+          <t>«Обычно спрашивают, какой способ запоминания самый лучший. Но дело чаще не в способе. У тех, у кого знаки не держатся, почти всегда одно и то же. Первое: человек узнал знак в тексте — и решил, что выучил. Второе: он учит знаки по одному…»</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>ДВА ПРЕДЛОГА ПОДРЯД, читается тяжело</t>
+          <t>ЗАКАЗЧИК: в одном абзаце четыре мысли и придаточные внутри придаточных</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>ТА ЖЕ ОШИБКА В УЖЕ СДАННОЙ СТАТЬЕ ПРО МОСКВУ</t>
+          <t>«одиночному знаку не за что зацепиться»</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Поправлена и там</t>
+          <t>«Отдельный знак почти ничего не значит, а слово значит»</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Адреса картинок Tilda при этом сохранены, блок пересобран</t>
+          <t>МЕТАФОРА на месте обычного глагола</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Проверка на метафоры</t>
+          <t>«Знак, выученный в одиночку, в памяти висит ни на чём. Слово даёт ему место»</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Пройдена</t>
+          <t>«Отдельный знак сам по себе почти ничего не значит, поэтому и запоминается плохо. А у слова есть перевод, звучание и случай, в котором его говорят»</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Метафор на месте обычных глаголов нет, слово «спотыкаются» отсутствует</t>
+          <t>МЕТАФОРА</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>ПИСАЛОСЬ СРАЗУ ПО НОВОМУ ПРАВИЛУ</t>
+          <t>«Это и есть тот перелом, ради которого стоит продержаться»</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Длинное простое предложение лучше короткого свёрнутого</t>
+          <t>«Ради этого и стоит продержаться первые месяцы»</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Перечисления — глаголами, а не цепочкой существительных. Правило записано после правок статьи про Москву</t>
+          <t>МЕТАФОРА</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>«знаки в слове ведут себя странно и разъезжаются»</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>«знаки расходятся и между ними встаёт что-то ещё»</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Знаки не «ведут себя»</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>«изменилось только то, в каком виде они лежали в голове»</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>«Изменилось только то, как он их выучил»</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Закручено</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>«не подряд, а с растущими промежутками»</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>«не подряд, а с перерывами, которые каждый раз становятся длиннее»</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>«Растущие промежутки» — термин, а не речь</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>«Знаки запоминаются не от количества подходов, а от того, что вы с ними делаете»</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>«Дело не в том, сколько раз вы написали знак, а в том, как вы его написали»</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Абстрактно</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>«обещания обратного стоит обходить стороной»</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>«тем, кто обещает обратное, верить не стоит»</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Книжный оборот</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>«печатают китайцы по звучанию, знак выбирается из списка»</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>«в телефоне и на компьютере знаки набирают по звучанию и выбирают из списка»</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Инверсия «печатают китайцы» читается тяжело</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>ТРИ МЕТАФОРЫ ПРОШЛИ ПЕРВУЮ ВЫЧИТКУ</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>«не за что зацепиться», «висит ни на чём», «перелом»</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Проверка на метафоры теперь идёт отдельным поиском по готовому файлу, как и слово «спотыкаются»</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>«в разборе ПРО ЗА какое время реально выучить китайский»</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>«в разборе о том, за какое время реально выучить китайский»</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>ДВА ПРЕДЛОГА ПОДРЯД</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>ТА ЖЕ ОШИБКА В СТАТЬЕ ПРО МОСКВУ</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Поправлена и там</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Адреса картинок Tilda сохранены, блок пересобран</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>ВСЕГО ПЕРЕПИСАНО</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Двадцать мест</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Правило прежнее: длинное простое предложение лучше короткого свёрнутого</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1762,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>39 045 знаков</t>
+          <t>39 114 знаков</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1786,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Инфографика 26,1 %, «Из личного опыта» 36,7 %, FAQ 65,8 %</t>
+          <t>Инфографика 26,2 %, «Из личного опыта» 37,0 %, FAQ 66,0 %</t>
         </is>
       </c>
     </row>
